--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -1068,7 +1068,7 @@
     <t>The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>refer dosageInstruction mapping</t>
   </si>
 </sst>
 </file>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -382,7 +382,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -516,7 +516,7 @@
     <t>MedicationStatement.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|CarePlan|ServiceRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.3.0|CarePlan|4.3.0|ServiceRequest|4.3.0)
 </t>
   </si>
   <si>
@@ -538,7 +538,7 @@
     <t>MedicationStatement.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Observation)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.3.0|MedicationDispense|4.3.0|MedicationStatement|4.3.0|Procedure|4.3.0|Observation|4.3.0)
 </t>
   </si>
   <si>
@@ -610,7 +610,7 @@
     <t>A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.3.0</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -634,7 +634,7 @@
     <t>A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-statement-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.3.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -712,7 +712,7 @@
     <t>MedicationStatement.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.3.0|EpisodeOfCare|4.3.0)
 </t>
   </si>
   <si>
@@ -890,7 +890,7 @@
     <t>MedicationStatement.informationSource</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Patient|4.3.0|Practitioner|4.3.0|PractitionerRole|4.3.0|RelatedPerson|4.3.0|Organization|4.3.0)
 </t>
   </si>
   <si>
@@ -906,7 +906,7 @@
     <t>MedicationStatement.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -937,7 +937,7 @@
     <t>A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1014,7 +1014,7 @@
     <t>MedicationStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.3.0|Observation|4.3.0|DiagnosticReport|4.3.0)
 </t>
   </si>
   <si>
@@ -1377,17 +1377,17 @@
   <dimension ref="A1:AN36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.7578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.7890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.8203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.8046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.70703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="105.265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1396,26 +1396,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="124.08984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.25" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="106.38671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="140.73046875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="120.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationstatement.xlsx
@@ -271,7 +271,16 @@
     <t>患者が薬剤を服用している状況についての情報である。</t>
   </si>
   <si>
-    <t>When interpreting a medicationStatement, the value of the status and NotTaken needed to be considered:+    <t>薬物測定を解釈するとき、ステータスの価値とNottakenを考慮する必要があります。+dedicationStatement.status + decutionStatement.wasnottaken+ステータス=アクティブ + nottaken = t =現在取得していない+ステータス=完了 + nottaken = t =過去に撮影されていない+status = dented + nottaken = t =取得する意図はありません+ステータス=アクティブ + nottaken = f =撮影ですが、規定されていない+ステータス=アクティブ + nottaken = f =撮影+status = dented +nottaken = f =は取得されます（開始されません）+ステータス=完了 + nottaken = f =過去に撮影+status = in error + nottaken = n/a =エラー。 / When interpreting a medicationStatement, the value of the status and NotTaken needed to be considered: MedicationStatement.status + MedicationStatement.wasNotTaken Status=Active + NotTaken=T = Not currently taking Status=Completed + NotTaken=T = Not taken in the past@@ -283,8 +292,8 @@
 Status=In Error + NotTaken=N/A = In Error.</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -309,13 +318,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -328,16 +337,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -348,13 +357,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -367,19 +376,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -399,13 +408,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -425,19 +434,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -455,33 +464,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationStatement.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -520,13 +530,13 @@
 </t>
   </si>
   <si>
-    <t>Fulfils plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+    <t>計画、提案、または命令を満たします / Fulfils plan, proposal or order</t>
+  </si>
+  <si>
+    <t>このイベントによって全体または一部に満たされる計画、提案、または命令。 / A plan, proposal or order that is fulfilled in whole or in part by this event.</t>
+  </si>
+  <si>
+    <t>イベントの許可を追跡し、提案/勧告が行われたかどうかを追跡することができます。 / Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -542,13 +552,13 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular event is a component or step.</t>
-  </si>
-  <si>
-    <t>This should not be used when indicating which resource a MedicationStatement has been derived from.  If that is the use case, then MedicationStatement.derivedFrom should be used.</t>
+    <t>参照イベントの一部 / Part of referenced event</t>
+  </si>
+  <si>
+    <t>この特定のイベントがコンポーネントまたはステップであるより大きなイベント。 / A larger event of which this particular event is a component or step.</t>
+  </si>
+  <si>
+    <t>これは、薬物測定がどのリソースから導出されているかを示す場合は使用しないでください。それがユースケースである場合、secticationStatement.derivedfromを使用する必要があります。 / This should not be used when indicating which resource a MedicationStatement has been derived from.  If that is the use case, then MedicationStatement.derivedFrom should be used.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -560,7 +570,7 @@
     <t>MedicationStatement.status</t>
   </si>
   <si>
-    <t>active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
+    <t>アクティブ | 完了 | エラー入力 | 意図的 | 停止 | 保留 | 不明 | 未取得 / active | completed | entered-in-error | intended | stopped | on-hold | unknown | not-taken</t>
   </si>
   <si>
     <t>服薬状況のを示す。コード表： http://hl7.org/fhir/CodeSystem/medication-statement-status
@@ -573,7 +583,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept indicating the current status of a MedicationStatement.</t>
+    <t>薬剤の現在の状態を示すコード化された概念。 / A coded concept indicating the current status of a MedicationStatement.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-statement-status|4.3.0</t>
@@ -607,7 +617,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>A coded concept indicating the reason for the status of the statement.</t>
+    <t>ステートメントのステータスの理由を示すコード化された概念。 / A coded concept indicating the reason for the status of the statement.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reason-medication-status-codes|4.3.0</t>
@@ -631,7 +641,7 @@
 HL7 FHIRではvalue setとして http://terminology.hl7.org/CodeSystem/medicationrequest-category がデフォルトで用いられるが、日本での使用の場合持参薬をカバーする必要があり、JAHIS処方データ規約V3.0Cに記載されているMERIT-9処方オーダ表7とJHSP0007表を組み合わせて持ちいることとする</t>
   </si>
   <si>
-    <t>A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
+    <t>薬剤が含まれている場所を識別するコード化された概念は、薬物測定に含まれる場所が消費または投与されると予想されます。 / A coded concept identifying where the medication included in the MedicationStatement is expected to be consumed or administered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medication-statement-category|4.3.0</t>
@@ -716,10 +726,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter / Episode associated with MedicationStatement</t>
-  </si>
-  <si>
-    <t>The encounter or episode of care that establishes the context for this MedicationStatement.</t>
+    <t>MedicationStatementに関連するEncounter / Episode / Encounter / Episode associated with MedicationStatement</t>
+  </si>
+  <si>
+    <t>この薬物測定のコンテキストを確立するEnounterまたはケアのエピソード。 / The encounter or episode of care that establishes the context for this MedicationStatement.</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -735,13 +745,13 @@
 Period</t>
   </si>
   <si>
-    <t>The date/time or interval when the medication is/was/will be taken</t>
-  </si>
-  <si>
-    <t>The interval of time during which it is being asserted that the patient is/was/will be taking the medication (or was not taking, when the MedicationStatement.taken element is No).</t>
-  </si>
-  <si>
-    <t>This attribute reflects the period over which the patient consumed the medication and is expected to be populated on the majority of Medication Statements. If the medication is still being taken at the time the statement is recorded, the "end" date will be omitted.  The date/time attribute supports a variety of dates - year, year/month and exact date.  If something more than this is required, this should be conveyed as text.</t>
+    <t>薬が服用/服用/服用/時刻または間隔 / The date/time or interval when the medication is/was/will be taken</t>
+  </si>
+  <si>
+    <t>患者が薬を服用している/服用している/（または薬を服用していなかった）と主張されている時間の間隔。 / The interval of time during which it is being asserted that the patient is/was/will be taking the medication (or was not taking, when the MedicationStatement.taken element is No).</t>
+  </si>
+  <si>
+    <t>この属性は、患者が投薬を消費した期間を反映しており、投薬声明の大部分に埋め込むことが期待されています。声明が記録された時点で薬がまだ撮影されている場合、「終了」日付は省略されます。日付/時刻属性は、年、年/月、正確な日付のさまざまな日付をサポートしています。これ以上のものが必要な場合は、これをテキストとして伝える必要があります。 / This attribute reflects the period over which the patient consumed the medication and is expected to be populated on the majority of Medication Statements. If the medication is still being taken at the time the statement is recorded, the "end" date will be omitted.  The date/time attribute supports a variety of dates - year, year/month and exact date.  If something more than this is required, this should be conveyed as text.</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -782,10 +792,10 @@
     <t>MedicationStatement.effective[x].id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -800,7 +810,7 @@
     <t>MedicationStatement.effective[x].extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -829,7 +839,7 @@
     <t>薬の服用を開始した日</t>
   </si>
   <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
+    <t>低要素が欠落している場合、意味は低い境界が知られていないことです。 / If the low element is missing, the meaning is that the low boundary is not known.</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -860,7 +870,7 @@
     <t>この値は必ず境界日を含む。2012-02-03T10:00:00は2012-02-03を終了時刻(end)の値とする期間を示す。</t>
   </si>
   <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
+    <t>期間の終了が欠落している場合、それは期間が進行中であることを意味します / If the end of the period is missing, it means that the period is ongoing</t>
   </si>
   <si>
     <t>Period.end</t>
@@ -916,7 +926,7 @@
     <t>MedicationStatementリソースと関連するMedicationRequestやその他の支持情報を表すリソースと関連付けられるようにする。</t>
   </si>
   <si>
-    <t>Likely references would be to MedicationRequest, MedicationDispense, Claim, Observation or QuestionnaireAnswers.  The most common use cases for deriving a MedicationStatement comes from creating a MedicationStatement from a MedicationRequest or from a lab observation or a claim.  it should be noted that the amount of information that is available varies from the type resource that you derive the MedicationStatement from.</t>
+    <t>おそらく参考文献は、薬物療法、薬剤、請求、観察、またはアンケート担当者に関するものです。薬物測定を導き出すための最も一般的なユースケースは、薬物療法または実験室の観察または請求からの薬物測定の作成に由来しています。利用可能な情報の量は、投薬手段を導き出すタイプリソースから異なることに注意する必要があります。 / Likely references would be to MedicationRequest, MedicationDispense, Claim, Observation or QuestionnaireAnswers.  The most common use cases for deriving a MedicationStatement comes from creating a MedicationStatement from a MedicationRequest or from a lab observation or a claim.  it should be noted that the amount of information that is available varies from the type resource that you derive the MedicationStatement from.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=SPRT]/target[classCode=ACT,moodCode=EVN]</t>
@@ -934,7 +944,7 @@
     <t>このコードは疾患分類であっても良い。JP Coreでは傷病名マスターの使用を前提とする。</t>
   </si>
   <si>
-    <t>A coded concept identifying why the medication is being taken.</t>
+    <t>薬が服用されている理由を特定するコード化された概念。 / A coded concept identifying why the medication is being taken.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-code|4.3.0</t>
@@ -965,13 +975,13 @@
     <t>投与理由，対象疾患についてのコード</t>
   </si>
   <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -990,16 +1000,16 @@
 </t>
   </si>
   <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -1021,10 +1031,10 @@
     <t>服薬理由を支持するObservation, Condition, DiagnosticReportについての参照。</t>
   </si>
   <si>
-    <t>Condition or observation that supports why the medication is being/was taken.</t>
-  </si>
-  <si>
-    <t>This is a reference to a condition that is the reason why the medication is being/was taken.  If only a code exists, use reasonForUseCode.</t>
+    <t>薬が摂取されている理由をサポートする状態または観察。 / Condition or observation that supports why the medication is being/was taken.</t>
+  </si>
+  <si>
+    <t>これは、薬が服用されている/服用されている理由である状態への言及です。コードのみが存在する場合は、ReasonForUseCodeを使用してください。 / This is a reference to a condition that is the reason why the medication is being/was taken.  If only a code exists, use reasonForUseCode.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1065,7 +1075,7 @@
     <t>患者にこの薬剤がどのように服用すべきかを示す情報</t>
   </si>
   <si>
-    <t>The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
+    <t>投薬声明の投与量に含まれる日付は、特定の用量の日付を反映しています。たとえば、「2016年11月1日から2016年11月3日まで、毎日1錠を服用し、2016年11月4日から2016年11月7日まで、毎日2錠を服用してください。」この特異性は、患者が標識容器を持ち込む場合、または薬物療法の声明が薬物療法に由来する場合にのみ居住することが予想されます。 / The dates included in the dosage on a Medication Statement reflect the dates for a given dose.  For example, "from November 1, 2016 to November 3, 2016, take one tablet daily and from November 4, 2016 to November 7, 2016, take two tablets daily."  It is expected that this specificity may only be populated where the patient brings in their labeled container or where the Medication Statement is derived from a MedicationRequest.</t>
   </si>
   <si>
     <t>refer dosageInstruction mapping</t>
@@ -1401,7 +1411,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="106.38671875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="161.6796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
